--- a/tests/fixtures/avance_badie_minimal.xlsx
+++ b/tests/fixtures/avance_badie_minimal.xlsx
@@ -11,6 +11,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cober_gen" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cober_marca" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Avance" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CuposVolumen" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CuposCoberGen" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CuposCober" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -639,4 +642,132 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>PREVENTISTA</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>GENERICO</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>DESAGREGADO</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cupo </t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ruta</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Preventista</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Generico</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ZONA</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CUPO </t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ruta</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Descripción Vendedor</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>MARCA</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ZONA</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CUPO </t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>